--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:08:21+00:00</t>
+    <t>2026-06-25T08:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:44:50+00:00</t>
+    <t>2026-06-25T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:51:35+00:00</t>
+    <t>2026-06-26T10:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>eyecolor</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/EyeColor|1.0.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/EyeColor|0.1.0}
 </t>
   </si>
   <si>
@@ -865,7 +865,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/ModifiedAdministrativeGender|1.0.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/ModifiedAdministrativeGender|0.1.0</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:11:25+00:00</t>
+    <t>2026-06-29T08:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:14:08+00:00</t>
+    <t>2026-06-29T08:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:25:33+00:00</t>
+    <t>2026-06-29T08:30:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:30:47+00:00</t>
+    <t>2026-06-30T06:46:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T06:46:17+00:00</t>
+    <t>2026-06-30T07:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:33:29+00:00</t>
+    <t>2026-06-30T12:30:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
+++ b/PageAccueil/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T12:30:50+00:00</t>
+    <t>2026-07-01T07:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
